--- a/Side Bar Files/GWD Data/HDPE Pipe PRICE.xlsx
+++ b/Side Bar Files/GWD Data/HDPE Pipe PRICE.xlsx
@@ -708,7 +708,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_4" displayName="Table_4" ref="A1:D78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_6" displayName="Table_6" ref="A1:D78">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -1015,7 +1015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129A2372-A430-4089-90A8-D15F89A1B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58366844-5518-4B5B-8DF2-DBF50CB0B9A7}">
   <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
